--- a/public/templates/인사기록 양식.xlsx
+++ b/public/templates/인사기록 양식.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>근무시작일, 근무종료일, 상위부서명</t>
+          <t>근무시작일, 근무종료일, 상위부서명. 이 열을 지우거나 모두 비워 두면 업로드 버튼 아래에 무엇이 빠졌는지 알려 줍니다.</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>첫 번째 시트만 읽습니다. 이 안내 시트는 지우지 않아도 읽지 않습니다.</t>
+          <t>꼭 있어야 하는 열이 있는 시트를 찾아 읽습니다. 이 안내 시트는 지우지 않아도 읽지 않습니다.</t>
         </is>
       </c>
     </row>

--- a/public/templates/인사기록 양식.xlsx
+++ b/public/templates/인사기록 양식.xlsx
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -581,9 +581,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -652,7 +650,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>근무시작일, 근무종료일, 상위부서명. 이 열을 지우거나 모두 비워 두면 업로드 버튼 아래에 무엇이 빠졌는지 알려 줍니다.</t>
+          <t>근무시작일, 근무종료일, 상위부서명. 이 열을 지우거나 근무시작일·상위부서명을 모두 비워 두면 업로드 버튼 아래에 무엇이 빠졌는지 알려 줍니다. 근무종료일 빈칸은 지금 근무 중으로 봅니다.</t>
         </is>
       </c>
     </row>
@@ -676,7 +674,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2024.01.01, 2024-01-01, 20240101 모양 모두 읽습니다. 지금 근무 중이면 근무종료일을 비워 둡니다.</t>
+          <t>2024.01.01, 2024-01-01, 20240101 모양과 엑셀 날짜 칸 모두 읽습니다. 지금 근무 중이면 근무종료일을 비워 둡니다. 없는 날짜를 적으면 빈칸으로 읽어 근무 중으로 보니 주의해 주세요.</t>
         </is>
       </c>
     </row>
@@ -688,7 +686,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>소속부서명이 지원정보 경력의 부서명과 같은 줄 가운데, 직위명이 실장·센터장·단장·본부장·부원장·원장으로 끝나는 사람을 부서장으로 봅니다. 여럿이면 지원자 근무 기간과 겹치는 사람 가운데 근무종료일이 가장 늦은 사람(근무종료일이 비어 있으면 지금 근무 중으로 봄)을 고릅니다. 겹치는 사람이 없으면 부서장 전체에서 같은 방법으로 고릅니다.</t>
+          <t>소속부서명이 지원정보 경력의 부서명과 같은(띄어쓰기·괄호·점 무시) 줄 가운데, 직위명이 실장·센터장·단장·본부장·부원장·원장으로 끝나는 사람을 부서장으로 봅니다. 여럿이면 지원자 근무 기간과 겹치는 사람 가운데 근무종료일이 가장 늦은 사람(근무종료일이 비어 있으면 지금 근무 중으로 봄)을 고릅니다. 겹치는 사람이 없으면 부서장 전체에서 같은 방법으로 고릅니다.</t>
         </is>
       </c>
     </row>
@@ -700,29 +698,41 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>상위부서명 열이 있으면 그 부서의 부서장을 상위부서장으로 찾습니다. 없으면 상위부서장은 표시하지 않습니다.</t>
+          <t>상위부서명이 적혀 있으면, 그 이름을 소속부서명으로 가진 줄에서 부서장 찾기와 같은 방법으로 상위부서장을 찾습니다. 같은 부서에 상위부서명이 여러 개 적혀 있으면 위쪽 줄의 것을 씁니다. 상위부서명 열이 없거나 모두 비어 있으면 상위부서장은 표시하지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>시트</t>
+          <t>제척 기간</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>꼭 있어야 하는 열이 있는 시트를 찾아 읽습니다. 이 안내 시트는 지우지 않아도 읽지 않습니다.</t>
+          <t>지원자가 그 부서에서 근무를 마친 날(지원정보 재직일자의 끝)이 평가기준일 기준 최근 2년 안이면 부서장·상위부서장을 제척합니다. 그보다 오래된 근무는 부서장을 보여 주기만 하고 제척으로 세지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>시트</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>꼭 있어야 하는 열이 있는 시트를 찾아 읽습니다. 이 안내 시트는 지우지 않아도 읽지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t>파일 형식</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>xlsx 또는 csv. 옛 엑셀 형식(.xls)은 xlsx 로 저장해 올려 주세요.</t>
         </is>
